--- a/examples/EXCEL/TestTable.xlsx
+++ b/examples/EXCEL/TestTable.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>TestColumn</t>
+  </si>
+  <si>
+    <t>Test23</t>
   </si>
   <si>
     <t>TestType</t>
@@ -430,19 +433,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -466,22 +473,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/examples/EXCEL/TestTable.xlsx
+++ b/examples/EXCEL/TestTable.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -23,6 +23,9 @@
     <t>Test23</t>
   </si>
   <si>
+    <t>Test45</t>
+  </si>
+  <si>
     <t>TestType</t>
   </si>
   <si>
@@ -33,6 +36,9 @@
   </si>
   <si>
     <t>TestType_Test2</t>
+  </si>
+  <si>
+    <t>TestType_Test3</t>
   </si>
 </sst>
 </file>
@@ -433,15 +439,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,12 +456,15 @@
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (TestType)" sqref="B2:B10000">
-      <formula1>'_DropDown'!$A$2:$A$4</formula1>
+      <formula1>'_DropDown'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -465,7 +474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -473,22 +482,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/examples/EXCEL/TestTable.xlsx
+++ b/examples/EXCEL/TestTable.xlsx
@@ -5,14 +5,16 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="GoTest" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="_DropDown" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="NameTest" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="_DropDown" state="veryHidden" r:id="rId6"/>
+    <sheet sheetId="4" name="_DataManager" state="veryHidden" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -26,6 +28,9 @@
     <t>Test45</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>TestType</t>
   </si>
   <si>
@@ -39,6 +44,12 @@
   </si>
   <si>
     <t>TestType_Test3</t>
+  </si>
+  <si>
+    <t>DataManager.ExcelMetadata</t>
+  </si>
+  <si>
+    <t>{"magic":"DataManager.ExcelMetadata","version":1,"sourceFile":"TestTable.proto","fingerprint":"dm1-80045915","tables":[{"messageName":"GoTest","memoColumns":[]},{"messageName":"NameTest","memoColumns":[]}]}</t>
   </si>
 </sst>
 </file>
@@ -94,10 +105,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -447,7 +458,7 @@
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,8 +473,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (TestType)" sqref="B2:B10000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="잘못된 값" error="정의된 Enum 값을 선택하세요. (TestType)" sqref="B2:B10001">
       <formula1>'_DropDown'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -473,6 +485,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -482,27 +518,51 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
